--- a/SpotCart_Appium_Mobile_E2E_Test_Report.xlsx
+++ b/SpotCart_Appium_Mobile_E2E_Test_Report.xlsx
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Automated Execution Timestamp: 2026-07-28 14:19:15 | Target: Android App (com.example.spotcart)</t>
+          <t>Automated Execution Timestamp: 2026-07-30 09:03:38 | Target: Android App (com.example.spotcart)</t>
         </is>
       </c>
     </row>

--- a/SpotCart_Appium_Mobile_E2E_Test_Report.xlsx
+++ b/SpotCart_Appium_Mobile_E2E_Test_Report.xlsx
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Automated Execution Timestamp: 2026-07-30 09:03:38 | Target: Android App (com.example.spotcart)</t>
+          <t>Automated Execution Timestamp: 2026-07-30 09:17:22 | Target: Android App (com.example.spotcart)</t>
         </is>
       </c>
     </row>
